--- a/artfynd/A 46868-2024 artfynd.xlsx
+++ b/artfynd/A 46868-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150148</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 46868-2024 artfynd.xlsx
+++ b/artfynd/A 46868-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,210 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121418010</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91967</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svegardammen, Svegardammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>481688</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6853679</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121417798</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91967</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svegardammen, Svegardammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>481725</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6853652</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46868-2024 artfynd.xlsx
+++ b/artfynd/A 46868-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150148</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121418010</v>
+        <v>121417798</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>91979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481688</v>
+        <v>481725</v>
       </c>
       <c r="R3" t="n">
-        <v>6853679</v>
+        <v>6853652</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121417798</v>
+        <v>121418010</v>
       </c>
       <c r="B4" t="n">
-        <v>91967</v>
+        <v>91979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481725</v>
+        <v>481688</v>
       </c>
       <c r="R4" t="n">
-        <v>6853652</v>
+        <v>6853679</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 46868-2024 artfynd.xlsx
+++ b/artfynd/A 46868-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150148</v>
       </c>
       <c r="B2" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121417798</v>
+        <v>121418010</v>
       </c>
       <c r="B3" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481725</v>
+        <v>481688</v>
       </c>
       <c r="R3" t="n">
-        <v>6853652</v>
+        <v>6853679</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121418010</v>
+        <v>121417798</v>
       </c>
       <c r="B4" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481688</v>
+        <v>481725</v>
       </c>
       <c r="R4" t="n">
-        <v>6853679</v>
+        <v>6853652</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 46868-2024 artfynd.xlsx
+++ b/artfynd/A 46868-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150148</v>
       </c>
       <c r="B2" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121418010</v>
+        <v>121417798</v>
       </c>
       <c r="B3" t="n">
-        <v>91980</v>
+        <v>91983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481688</v>
+        <v>481725</v>
       </c>
       <c r="R3" t="n">
-        <v>6853679</v>
+        <v>6853652</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121417798</v>
+        <v>121418010</v>
       </c>
       <c r="B4" t="n">
-        <v>91980</v>
+        <v>91983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481725</v>
+        <v>481688</v>
       </c>
       <c r="R4" t="n">
-        <v>6853652</v>
+        <v>6853679</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 46868-2024 artfynd.xlsx
+++ b/artfynd/A 46868-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121417798</v>
       </c>
       <c r="B3" t="n">
-        <v>91983</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>121418010</v>
       </c>
       <c r="B4" t="n">
-        <v>91983</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46868-2024 artfynd.xlsx
+++ b/artfynd/A 46868-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121417798</v>
+        <v>121418010</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>91990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481725</v>
+        <v>481688</v>
       </c>
       <c r="R3" t="n">
-        <v>6853652</v>
+        <v>6853679</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121418010</v>
+        <v>121417798</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
+        <v>91990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481688</v>
+        <v>481725</v>
       </c>
       <c r="R4" t="n">
-        <v>6853679</v>
+        <v>6853652</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 46868-2024 artfynd.xlsx
+++ b/artfynd/A 46868-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121418010</v>
+        <v>121417798</v>
       </c>
       <c r="B3" t="n">
         <v>91990</v>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481688</v>
+        <v>481725</v>
       </c>
       <c r="R3" t="n">
-        <v>6853679</v>
+        <v>6853652</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121417798</v>
+        <v>121418010</v>
       </c>
       <c r="B4" t="n">
         <v>91990</v>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481725</v>
+        <v>481688</v>
       </c>
       <c r="R4" t="n">
-        <v>6853652</v>
+        <v>6853679</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 46868-2024 artfynd.xlsx
+++ b/artfynd/A 46868-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121417798</v>
+        <v>121418010</v>
       </c>
       <c r="B3" t="n">
-        <v>91990</v>
+        <v>91998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481725</v>
+        <v>481688</v>
       </c>
       <c r="R3" t="n">
-        <v>6853652</v>
+        <v>6853679</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121418010</v>
+        <v>121417798</v>
       </c>
       <c r="B4" t="n">
-        <v>91990</v>
+        <v>91998</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481688</v>
+        <v>481725</v>
       </c>
       <c r="R4" t="n">
-        <v>6853679</v>
+        <v>6853652</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
